--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558545.8759492313</v>
+        <v>558546</v>
       </c>
       <c r="R9" t="n">
-        <v>6840125.984908893</v>
+        <v>6840126</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,19 +1607,9 @@
           <t>2021-04-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-04-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,12 +1625,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1625,12 +1625,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1517,7 +1517,7 @@
         <v>92763517</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,6 +1756,125 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125319123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98135</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gruvvägen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558529</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6839763</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carina Frost</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carina Frost, Jenss Hansen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>125319123</v>
       </c>
       <c r="B11" t="n">
-        <v>98135</v>
+        <v>98303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>125319123</v>
       </c>
       <c r="B11" t="n">
-        <v>98358</v>
+        <v>98365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carina Frost, Jenss Hansen</t>
+          <t>Jenss Hansen, Carina Frost</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>125319123</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jenss Hansen, Carina Frost</t>
+          <t>Carina Frost, Jenss Hansen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 69572-2020 artfynd.xlsx
+++ b/artfynd/A 69572-2020 artfynd.xlsx
@@ -1761,7 +1761,7 @@
         <v>125319123</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
